--- a/3-能力管理/运行记录类文件/JXTX-03-03-运维服务能力管理指标体系.xlsx
+++ b/3-能力管理/运行记录类文件/JXTX-03-03-运维服务能力管理指标体系.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9575"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="KPI指标体系" sheetId="1" r:id="rId1"/>
@@ -371,7 +371,7 @@
     <t>服务数据分析利用次数</t>
   </si>
   <si>
-    <t>≥次</t>
+    <t>≥3次</t>
   </si>
   <si>
     <t>数量，服务数据分析使用报告数</t>

--- a/3-能力管理/运行记录类文件/JXTX-03-03-运维服务能力管理指标体系.xlsx
+++ b/3-能力管理/运行记录类文件/JXTX-03-03-运维服务能力管理指标体系.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="KPI指标体系" sheetId="1" r:id="rId1"/>
@@ -1178,22 +1178,22 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1456690</xdr:colOff>
+      <xdr:colOff>40640</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>8890</xdr:rowOff>
+      <xdr:rowOff>34925</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1351280" cy="296545"/>
+    <xdr:ext cx="1845945" cy="252730"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp>
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="文本框 4"/>
+            <xdr:cNvPr id="2" name="文本框 1"/>
             <xdr:cNvSpPr txBox="1"/>
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5175250" y="799465"/>
-              <a:ext cx="1351280" cy="296545"/>
+              <a:off x="3759200" y="825500"/>
+              <a:ext cx="1845945" cy="252730"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1226,34 +1226,6 @@
               </a:r>
               <a14:m>
                 <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:f>
-                    <m:fPr>
-                      <m:ctrlPr>
-                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                        </a:rPr>
-                      </m:ctrlPr>
-                    </m:fPr>
-                    <m:num>
-                      <m:r>
-                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                        </a:rPr>
-                        <m:t>1</m:t>
-                      </m:r>
-                    </m:num>
-                    <m:den>
-                      <m:r>
-                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                        </a:rPr>
-                        <m:t>𝑛</m:t>
-                      </m:r>
-                    </m:den>
-                  </m:f>
                   <m:nary>
                     <m:naryPr>
                       <m:chr m:val="∑"/>
@@ -1322,8 +1294,97 @@
               </a14:m>
               <a:r>
                 <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
-                <a:t>)*100%</a:t>
+                <a:t>)/</a:t>
               </a:r>
+              <a14:m>
+                <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:r>
+                    <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
+                    <m:t>(</m:t>
+                  </m:r>
+                  <m:nary>
+                    <m:naryPr>
+                      <m:chr m:val="∑"/>
+                      <m:limLoc m:val="undOvr"/>
+                      <m:ctrlPr>
+                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                        </a:rPr>
+                      </m:ctrlPr>
+                    </m:naryPr>
+                    <m:sub>
+                      <m:r>
+                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                        </a:rPr>
+                        <m:t>𝑖</m:t>
+                      </m:r>
+                      <m:r>
+                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                        </a:rPr>
+                        <m:t>=</m:t>
+                      </m:r>
+                      <m:r>
+                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                        </a:rPr>
+                        <m:t>0</m:t>
+                      </m:r>
+                    </m:sub>
+                    <m:sup>
+                      <m:r>
+                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                        </a:rPr>
+                        <m:t>𝑛</m:t>
+                      </m:r>
+                    </m:sup>
+                    <m:e>
+                      <m:r>
+                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                        </a:rPr>
+                        <m:t>𝑘</m:t>
+                      </m:r>
+                      <m:r>
+                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                        </a:rPr>
+                        <m:t>)</m:t>
+                      </m:r>
+                      <m:r>
+                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                        </a:rPr>
+                        <m:t>∗</m:t>
+                      </m:r>
+                      <m:r>
+                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                        </a:rPr>
+                        <m:t>100</m:t>
+                      </m:r>
+                      <m:r>
+                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                        </a:rPr>
+                        <m:t>%</m:t>
+                      </m:r>
+                    </m:e>
+                  </m:nary>
+                </m:oMath>
+              </a14:m>
               <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100"/>
             </a:p>
           </xdr:txBody>
@@ -1332,13 +1393,13 @@
       <mc:Fallback>
         <xdr:sp>
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="文本框 4"/>
+            <xdr:cNvPr id="2" name="文本框 1"/>
             <xdr:cNvSpPr txBox="1"/>
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5175250" y="799465"/>
-              <a:ext cx="1351280" cy="296545"/>
+              <a:off x="3759200" y="825500"/>
+              <a:ext cx="1845945" cy="252730"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1368,27 +1429,6 @@
                   <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
                 </a:rPr>
                 <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>1</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>/</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>𝑛</a:t>
               </a:r>
               <a:r>
                 <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
@@ -1466,7 +1506,102 @@
               </a:r>
               <a:r>
                 <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
-                <a:t>)*100%</a:t>
+                <a:t>)/</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                </a:rPr>
+                <a:t>∑</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                </a:rPr>
+                <a:t>_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                </a:rPr>
+                <a:t>𝑖</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                </a:rPr>
+                <a:t>=</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                </a:rPr>
+                <a:t>0</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                </a:rPr>
+                <a:t>^</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                </a:rPr>
+                <a:t>𝑛</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                </a:rPr>
+                <a:t>▒</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                </a:rPr>
+                <a:t>𝑘</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                </a:rPr>
+                <a:t>)</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                </a:rPr>
+                <a:t>∗</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                </a:rPr>
+                <a:t>100</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
+                </a:rPr>
+                <a:t>%</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100"/>
             </a:p>

--- a/3-能力管理/运行记录类文件/JXTX-03-03-运维服务能力管理指标体系.xlsx
+++ b/3-能力管理/运行记录类文件/JXTX-03-03-运维服务能力管理指标体系.xlsx
@@ -4,15 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="23040" windowHeight="9060" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="KPI指标体系" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_GoBack" localSheetId="0">KPI指标体系!#REF!</definedName>
+    <definedName name="_GoBack" localSheetId="0">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -405,18 +405,25 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -424,42 +431,45 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="楷体_GB2312"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -467,6 +477,7 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -475,7 +486,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -483,6 +494,7 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -491,6 +503,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -499,6 +512,7 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -506,7 +520,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -514,7 +528,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -522,7 +536,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -530,14 +544,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -545,54 +559,245 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <name val="Cambria Math"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="37">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -612,192 +817,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -808,21 +827,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -838,7 +842,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -847,16 +850,14 @@
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -871,7 +872,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -886,7 +886,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -901,7 +900,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -910,7 +908,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -921,249 +918,350 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="35" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="36" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="54">
+    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Percent" xfId="15"/>
+    <cellStyle name="Currency" xfId="16"/>
+    <cellStyle name="Currency [0]" xfId="17"/>
+    <cellStyle name="Comma" xfId="18"/>
+    <cellStyle name="Comma [0]" xfId="19"/>
+    <cellStyle name="千位分隔" xfId="20"/>
+    <cellStyle name="货币" xfId="21"/>
+    <cellStyle name="百分比" xfId="22"/>
+    <cellStyle name="千位分隔[0]" xfId="23"/>
+    <cellStyle name="货币[0]" xfId="24"/>
+    <cellStyle name="超链接" xfId="25"/>
+    <cellStyle name="已访问的超链接" xfId="26"/>
+    <cellStyle name="注释" xfId="27"/>
+    <cellStyle name="警告文本" xfId="28"/>
+    <cellStyle name="标题" xfId="29"/>
+    <cellStyle name="解释性文本" xfId="30"/>
+    <cellStyle name="标题 1" xfId="31"/>
+    <cellStyle name="标题 2" xfId="32"/>
+    <cellStyle name="标题 3" xfId="33"/>
+    <cellStyle name="标题 4" xfId="34"/>
+    <cellStyle name="输入" xfId="35"/>
+    <cellStyle name="输出" xfId="36"/>
+    <cellStyle name="计算" xfId="37"/>
+    <cellStyle name="检查单元格" xfId="38"/>
+    <cellStyle name="链接单元格" xfId="39"/>
+    <cellStyle name="汇总" xfId="40"/>
+    <cellStyle name="好" xfId="41"/>
+    <cellStyle name="差" xfId="42"/>
+    <cellStyle name="适中" xfId="43"/>
+    <cellStyle name="强调文字颜色 1" xfId="44"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="45"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="46"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="47"/>
+    <cellStyle name="强调文字颜色 2" xfId="48"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="49"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="50"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="51"/>
+    <cellStyle name="强调文字颜色 3" xfId="52"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="53"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="54"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="55"/>
+    <cellStyle name="强调文字颜色 4" xfId="56"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="57"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="58"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="59"/>
+    <cellStyle name="强调文字颜色 5" xfId="60"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="61"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="62"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="63"/>
+    <cellStyle name="强调文字颜色 6" xfId="64"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="65"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="66"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="67"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
-    <mruColors>
-      <color rgb="00C0C0C0"/>
-    </mruColors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1174,7 +1272,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
@@ -1946,19 +2044,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="4.77777777777778" customWidth="1"/>
-    <col min="3" max="3" width="10.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="4.75" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="5" max="5" width="8.66666666666667" customWidth="1"/>
-    <col min="6" max="6" width="64.6851851851852" customWidth="1"/>
+    <col min="5" max="5" width="8.625" customWidth="1"/>
+    <col min="6" max="6" width="64.625" customWidth="1"/>
     <col min="7" max="7" width="10.5" customWidth="1"/>
-    <col min="8" max="8" width="17.4444444444444" customWidth="1"/>
+    <col min="8" max="8" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1" spans="1:8">
+    <row r="1" spans="1:8" ht="13.5" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1970,7 +2068,7 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:8">
+    <row r="2" spans="1:8" ht="24" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1980,7 +2078,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" ht="24.75" customHeight="1" spans="1:8">
+    <row r="3" spans="1:8" ht="24.75" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -2004,7 +2102,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" spans="1:8">
+    <row r="4" spans="1:8" ht="24" customHeight="1">
       <c r="A4" s="7">
         <f>ROW()-3</f>
         <v>1</v>
@@ -2027,9 +2125,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" ht="14.4">
       <c r="A5" s="7">
-        <f t="shared" ref="A5:A14" si="0">ROW()-3</f>
+        <f t="shared" si="0" ref="A5:A14">ROW()-3</f>
         <v>2</v>
       </c>
       <c r="B5" s="8"/>
@@ -2050,7 +2148,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" ht="14.4">
       <c r="A6" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2073,7 +2171,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" ht="14.4">
       <c r="A7" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2096,7 +2194,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" ht="14.4">
       <c r="A8" s="7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2123,7 +2221,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" ht="14.4">
       <c r="A9" s="7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2148,7 +2246,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" ht="14.4">
       <c r="A10" s="7">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2173,7 +2271,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" ht="14.4">
       <c r="A11" s="7">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2198,7 +2296,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" ht="14.4">
       <c r="A12" s="7">
         <v>9</v>
       </c>
@@ -2222,7 +2320,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" ht="14.4">
       <c r="A13" s="7">
         <f>ROW()-3</f>
         <v>10</v>
@@ -2247,7 +2345,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" ht="14.4">
       <c r="A14" s="7">
         <f>ROW()-3</f>
         <v>11</v>
@@ -2274,9 +2372,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" ht="14.4">
       <c r="A15" s="7">
-        <f t="shared" ref="A15:A24" si="1">ROW()-3</f>
+        <f t="shared" si="1" ref="A15:A24">ROW()-3</f>
         <v>12</v>
       </c>
       <c r="B15" s="8"/>
@@ -2299,7 +2397,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" ht="14.4">
       <c r="A16" s="7">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -2324,7 +2422,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" ht="14.4">
       <c r="A17" s="7">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -2349,7 +2447,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" ht="14.4">
       <c r="A18" s="7">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -2372,7 +2470,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" ht="14.4">
       <c r="A19" s="7">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -2397,7 +2495,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" ht="14.4">
       <c r="A20" s="7">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -2420,7 +2518,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" ht="14.4">
       <c r="A21" s="7">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -2445,7 +2543,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" ht="14.4">
       <c r="A22" s="7">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -2470,7 +2568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" ht="14.4">
       <c r="A23" s="7">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -2495,7 +2593,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" ht="14.4">
       <c r="A24" s="7">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -2520,9 +2618,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" ht="14.4">
       <c r="A25" s="7">
-        <f t="shared" ref="A25:A36" si="2">ROW()-3</f>
+        <f t="shared" si="2" ref="A25:A36">ROW()-3</f>
         <v>22</v>
       </c>
       <c r="B25" s="8"/>
@@ -2543,7 +2641,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" ht="14.4">
       <c r="A26" s="7">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -2568,7 +2666,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" ht="14.4">
       <c r="A27" s="7">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -2593,7 +2691,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="1:8">
+    <row r="28" spans="1:8" s="1" customFormat="1" ht="14.4">
       <c r="A28" s="7">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -2618,7 +2716,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" spans="1:8">
+    <row r="29" spans="1:8" s="1" customFormat="1" ht="14.4">
       <c r="A29" s="7">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -2641,7 +2739,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" spans="1:8">
+    <row r="30" spans="1:8" s="1" customFormat="1" ht="14.4">
       <c r="A30" s="7">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -2668,7 +2766,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" spans="1:8">
+    <row r="31" spans="1:8" s="1" customFormat="1" ht="14.4">
       <c r="A31" s="7">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -2693,7 +2791,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" spans="1:8">
+    <row r="32" spans="1:8" s="1" customFormat="1" ht="14.4">
       <c r="A32" s="7">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -2718,7 +2816,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" ht="14.4">
       <c r="A33" s="7">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -2743,7 +2841,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" ht="14.4">
       <c r="A34" s="7">
         <f t="shared" si="2"/>
         <v>31</v>
@@ -2768,7 +2866,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" ht="14.4">
       <c r="A35" s="7">
         <f t="shared" si="2"/>
         <v>32</v>
@@ -2793,7 +2891,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" ht="14.4">
       <c r="A36" s="7">
         <f t="shared" si="2"/>
         <v>33</v>
@@ -2834,7 +2932,7 @@
     <mergeCell ref="A1:H2"/>
   </mergeCells>
   <pageMargins left="0.707638888888889" right="0.511805555555556" top="0.747916666666667" bottom="0.747916666666667" header="0.313888888888889" footer="0.313888888888889"/>
-  <pageSetup paperSize="9" scale="92" fitToHeight="0" orientation="landscape"/>
+  <pageSetup fitToHeight="0" orientation="landscape" paperSize="9" scale="10"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/3-能力管理/运行记录类文件/JXTX-03-03-运维服务能力管理指标体系.xlsx
+++ b/3-能力管理/运行记录类文件/JXTX-03-03-运维服务能力管理指标体系.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="120" windowWidth="23040" windowHeight="9060" activeTab="0"/>
+    <workbookView windowWidth="22188" windowHeight="9575"/>
   </bookViews>
   <sheets>
     <sheet name="KPI指标体系" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
   <definedNames>
     <definedName name="_GoBack" localSheetId="0">#REF!</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -405,25 +405,18 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -431,45 +424,42 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="楷体_GB2312"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -477,7 +467,6 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -486,7 +475,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -494,7 +483,6 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -503,7 +491,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -512,7 +499,6 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -520,7 +506,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -528,7 +514,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -536,7 +522,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -544,14 +530,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -559,59 +545,76 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Cambria Math"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="37">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0C0C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -793,30 +796,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0C0C0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="22"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -827,6 +806,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -842,6 +836,7 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -850,6 +845,7 @@
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -858,6 +854,7 @@
       <bottom style="medium">
         <color theme="4" tint="0.49998"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -872,6 +869,7 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -886,6 +884,7 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -900,6 +899,7 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -908,6 +908,7 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -918,351 +919,160 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="68">
+  <cellStyleXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-      <protection/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="7" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="36" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="5" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="54">
-    <cellStyle name="Normal" xfId="0"/>
-    <cellStyle name="Percent" xfId="15"/>
-    <cellStyle name="Currency" xfId="16"/>
-    <cellStyle name="Currency [0]" xfId="17"/>
-    <cellStyle name="Comma" xfId="18"/>
-    <cellStyle name="Comma [0]" xfId="19"/>
-    <cellStyle name="千位分隔" xfId="20"/>
-    <cellStyle name="货币" xfId="21"/>
-    <cellStyle name="百分比" xfId="22"/>
-    <cellStyle name="千位分隔[0]" xfId="23"/>
-    <cellStyle name="货币[0]" xfId="24"/>
-    <cellStyle name="超链接" xfId="25"/>
-    <cellStyle name="已访问的超链接" xfId="26"/>
-    <cellStyle name="注释" xfId="27"/>
-    <cellStyle name="警告文本" xfId="28"/>
-    <cellStyle name="标题" xfId="29"/>
-    <cellStyle name="解释性文本" xfId="30"/>
-    <cellStyle name="标题 1" xfId="31"/>
-    <cellStyle name="标题 2" xfId="32"/>
-    <cellStyle name="标题 3" xfId="33"/>
-    <cellStyle name="标题 4" xfId="34"/>
-    <cellStyle name="输入" xfId="35"/>
-    <cellStyle name="输出" xfId="36"/>
-    <cellStyle name="计算" xfId="37"/>
-    <cellStyle name="检查单元格" xfId="38"/>
-    <cellStyle name="链接单元格" xfId="39"/>
-    <cellStyle name="汇总" xfId="40"/>
-    <cellStyle name="好" xfId="41"/>
-    <cellStyle name="差" xfId="42"/>
-    <cellStyle name="适中" xfId="43"/>
-    <cellStyle name="强调文字颜色 1" xfId="44"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="45"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="46"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="47"/>
-    <cellStyle name="强调文字颜色 2" xfId="48"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="49"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="50"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="51"/>
-    <cellStyle name="强调文字颜色 3" xfId="52"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="53"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="54"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="55"/>
-    <cellStyle name="强调文字颜色 4" xfId="56"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="57"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="58"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="59"/>
-    <cellStyle name="强调文字颜色 5" xfId="60"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="61"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="62"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="63"/>
-    <cellStyle name="强调文字颜色 6" xfId="64"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="65"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="66"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="67"/>
+  <cellStyles count="55">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="49"/>
+    <cellStyle name="Percent" xfId="50"/>
+    <cellStyle name="Currency" xfId="51"/>
+    <cellStyle name="Currency [0]" xfId="52"/>
+    <cellStyle name="Comma" xfId="53"/>
+    <cellStyle name="Comma [0]" xfId="54"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1272,443 +1082,49 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-  <xdr:oneCellAnchor>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>40640</xdr:colOff>
+      <xdr:colOff>69215</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>34925</xdr:rowOff>
+      <xdr:rowOff>34290</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1845945" cy="252730"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:sp>
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2" name="文本框 1"/>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3759200" y="825500"/>
-              <a:ext cx="1845945" cy="252730"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a14:m>
-                <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:nary>
-                    <m:naryPr>
-                      <m:chr m:val="∑"/>
-                      <m:limLoc m:val="undOvr"/>
-                      <m:ctrlPr>
-                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                        </a:rPr>
-                      </m:ctrlPr>
-                    </m:naryPr>
-                    <m:sub>
-                      <m:r>
-                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                        </a:rPr>
-                        <m:t>𝑖</m:t>
-                      </m:r>
-                      <m:r>
-                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                        </a:rPr>
-                        <m:t>=</m:t>
-                      </m:r>
-                      <m:r>
-                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                        </a:rPr>
-                        <m:t>0</m:t>
-                      </m:r>
-                    </m:sub>
-                    <m:sup>
-                      <m:r>
-                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                        </a:rPr>
-                        <m:t>𝑛</m:t>
-                      </m:r>
-                    </m:sup>
-                    <m:e>
-                      <m:r>
-                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                        </a:rPr>
-                        <m:t>𝑁</m:t>
-                      </m:r>
-                      <m:r>
-                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1" baseline="-25000">
-                          <a:solidFill>
-                            <a:schemeClr val="tx1"/>
-                          </a:solidFill>
-                          <a:uFillTx/>
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                        </a:rPr>
-                        <m:t>𝑖</m:t>
-                      </m:r>
-                    </m:e>
-                  </m:nary>
-                </m:oMath>
-              </a14:m>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
-                <a:t>)/</a:t>
-              </a:r>
-              <a14:m>
-                <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:r>
-                    <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
-                    <m:t>(</m:t>
-                  </m:r>
-                  <m:nary>
-                    <m:naryPr>
-                      <m:chr m:val="∑"/>
-                      <m:limLoc m:val="undOvr"/>
-                      <m:ctrlPr>
-                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                        </a:rPr>
-                      </m:ctrlPr>
-                    </m:naryPr>
-                    <m:sub>
-                      <m:r>
-                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                        </a:rPr>
-                        <m:t>𝑖</m:t>
-                      </m:r>
-                      <m:r>
-                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                        </a:rPr>
-                        <m:t>=</m:t>
-                      </m:r>
-                      <m:r>
-                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                        </a:rPr>
-                        <m:t>0</m:t>
-                      </m:r>
-                    </m:sub>
-                    <m:sup>
-                      <m:r>
-                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                        </a:rPr>
-                        <m:t>𝑛</m:t>
-                      </m:r>
-                    </m:sup>
-                    <m:e>
-                      <m:r>
-                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                        </a:rPr>
-                        <m:t>𝑘</m:t>
-                      </m:r>
-                      <m:r>
-                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                        </a:rPr>
-                        <m:t>)</m:t>
-                      </m:r>
-                      <m:r>
-                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                        </a:rPr>
-                        <m:t>∗</m:t>
-                      </m:r>
-                      <m:r>
-                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                        </a:rPr>
-                        <m:t>100</m:t>
-                      </m:r>
-                      <m:r>
-                        <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                          <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                        </a:rPr>
-                        <m:t>%</m:t>
-                      </m:r>
-                    </m:e>
-                  </m:nary>
-                </m:oMath>
-              </a14:m>
-              <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp>
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2" name="文本框 1"/>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3759200" y="825500"/>
-              <a:ext cx="1845945" cy="252730"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>∑</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>_</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>𝑖</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>=</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>0</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>^</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>𝑛</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>▒</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>𝑁</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100" baseline="-25000">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:uFillTx/>
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>𝑖</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
-                <a:t>)/</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>∑</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>_</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>𝑖</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>=</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>0</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>^</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>𝑛</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>▒</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>𝑘</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>)</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>∗</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>100</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                  <a:cs typeface="Cambria Math" panose="02040503050406030204" charset="0"/>
-                </a:rPr>
-                <a:t>%</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2246630</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>283210</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3781425" y="824865"/>
+          <a:ext cx="2177415" cy="248920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2044,875 +1460,875 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="9" style="2"/>
+    <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="4.75" customWidth="1"/>
     <col min="3" max="3" width="10.75" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="5" max="5" width="8.625" customWidth="1"/>
-    <col min="6" max="6" width="64.625" customWidth="1"/>
+    <col min="5" max="5" width="8.62962962962963" customWidth="1"/>
+    <col min="6" max="6" width="64.6296296296296" customWidth="1"/>
     <col min="7" max="7" width="10.5" customWidth="1"/>
     <col min="8" max="8" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" ht="13.5" customHeight="1" spans="1:8">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="2" spans="1:8" ht="24" customHeight="1">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:8">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" ht="24.75" customHeight="1" spans="1:8">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="24" customHeight="1">
-      <c r="A4" s="7">
+    <row r="4" ht="24" customHeight="1" spans="1:8">
+      <c r="A4" s="6">
         <f>ROW()-3</f>
         <v>1</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="9" t="s">
+      <c r="C4" s="7"/>
+      <c r="D4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9" t="s">
+      <c r="F4" s="8"/>
+      <c r="G4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="14.4">
-      <c r="A5" s="7">
-        <f t="shared" si="0" ref="A5:A14">ROW()-3</f>
+    <row r="5" spans="1:8">
+      <c r="A5" s="6">
+        <f t="shared" ref="A5:A14" si="0">ROW()-3</f>
         <v>2</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="9" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="14.4">
-      <c r="A6" s="7">
+    <row r="6" spans="1:8">
+      <c r="A6" s="6">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="9" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="14.4">
-      <c r="A7" s="7">
+    <row r="7" spans="1:8">
+      <c r="A7" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="9" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="14.4">
-      <c r="A8" s="7">
+    <row r="8" spans="1:8">
+      <c r="A8" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="14.4">
-      <c r="A9" s="7">
+    <row r="9" spans="1:8">
+      <c r="A9" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="14.4">
-      <c r="A10" s="7">
+    <row r="10" spans="1:8">
+      <c r="A10" s="6">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8" t="s">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="14.4">
-      <c r="A11" s="7">
+    <row r="11" spans="1:8">
+      <c r="A11" s="6">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8" t="s">
+      <c r="B11" s="7"/>
+      <c r="C11" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="14.4">
-      <c r="A12" s="7">
+    <row r="12" spans="1:8">
+      <c r="A12" s="6">
         <v>9</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8" t="s">
+      <c r="B12" s="7"/>
+      <c r="C12" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="14.4">
-      <c r="A13" s="7">
+    <row r="13" spans="1:8">
+      <c r="A13" s="6">
         <f>ROW()-3</f>
         <v>10</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8" t="s">
+      <c r="B13" s="7"/>
+      <c r="C13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="14.4">
-      <c r="A14" s="7">
+    <row r="14" spans="1:8">
+      <c r="A14" s="6">
         <f>ROW()-3</f>
         <v>11</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="14.4">
-      <c r="A15" s="7">
-        <f t="shared" si="1" ref="A15:A24">ROW()-3</f>
+    <row r="15" spans="1:8">
+      <c r="A15" s="6">
+        <f t="shared" ref="A15:A24" si="1">ROW()-3</f>
         <v>12</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8" t="s">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="14.4">
-      <c r="A16" s="7">
+    <row r="16" spans="1:8">
+      <c r="A16" s="6">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8" t="s">
+      <c r="B16" s="7"/>
+      <c r="C16" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="14.4">
-      <c r="A17" s="7">
+    <row r="17" spans="1:8">
+      <c r="A17" s="6">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8" t="s">
+      <c r="B17" s="7"/>
+      <c r="C17" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="14.4">
-      <c r="A18" s="7">
+    <row r="18" spans="1:8">
+      <c r="A18" s="6">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="9" t="s">
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="14.4">
-      <c r="A19" s="7">
+    <row r="19" spans="1:8">
+      <c r="A19" s="6">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8" t="s">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="14.4">
-      <c r="A20" s="7">
+    <row r="20" spans="1:8">
+      <c r="A20" s="6">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="9" t="s">
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="14.4">
-      <c r="A21" s="7">
+    <row r="21" spans="1:8">
+      <c r="A21" s="6">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8" t="s">
+      <c r="B21" s="7"/>
+      <c r="C21" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="14.4">
-      <c r="A22" s="7">
+    <row r="22" spans="1:8">
+      <c r="A22" s="6">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8" t="s">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="14.4">
-      <c r="A23" s="7">
+    <row r="23" spans="1:8">
+      <c r="A23" s="6">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8" t="s">
+      <c r="B23" s="7"/>
+      <c r="C23" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="H23" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="14.4">
-      <c r="A24" s="7">
+    <row r="24" spans="1:8">
+      <c r="A24" s="6">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8" t="s">
+      <c r="B24" s="7"/>
+      <c r="C24" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="14.4">
-      <c r="A25" s="7">
-        <f t="shared" si="2" ref="A25:A36">ROW()-3</f>
+    <row r="25" spans="1:8">
+      <c r="A25" s="6">
+        <f t="shared" ref="A25:A36" si="2">ROW()-3</f>
         <v>22</v>
       </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="9" t="s">
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="14.4">
-      <c r="A26" s="7">
+    <row r="26" spans="1:8">
+      <c r="A26" s="6">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8" t="s">
+      <c r="B26" s="7"/>
+      <c r="C26" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="14.4">
-      <c r="A27" s="7">
+    <row r="27" spans="1:8">
+      <c r="A27" s="6">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8" t="s">
+      <c r="B27" s="7"/>
+      <c r="C27" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H27" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:8" s="1" customFormat="1" ht="14.4">
-      <c r="A28" s="7">
+    <row r="28" customFormat="1" spans="1:8">
+      <c r="A28" s="6">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="9" t="s">
+      <c r="C28" s="7"/>
+      <c r="D28" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="29" spans="1:8" s="1" customFormat="1" ht="14.4">
-      <c r="A29" s="7">
+    <row r="29" customFormat="1" spans="1:8">
+      <c r="A29" s="6">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="9" t="s">
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="H29" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="30" spans="1:8" s="1" customFormat="1" ht="14.4">
-      <c r="A30" s="7">
+    <row r="30" customFormat="1" spans="1:8">
+      <c r="A30" s="6">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:8" s="1" customFormat="1" ht="14.4">
-      <c r="A31" s="7">
+    <row r="31" customFormat="1" spans="1:8">
+      <c r="A31" s="6">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8" t="s">
+      <c r="B31" s="7"/>
+      <c r="C31" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H31" s="9" t="s">
+      <c r="H31" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:8" s="1" customFormat="1" ht="14.4">
-      <c r="A32" s="7">
+    <row r="32" customFormat="1" spans="1:8">
+      <c r="A32" s="6">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8" t="s">
+      <c r="B32" s="7"/>
+      <c r="C32" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E32" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H32" s="9" t="s">
+      <c r="H32" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="14.4">
-      <c r="A33" s="7">
+    <row r="33" ht="28.8" spans="1:8">
+      <c r="A33" s="6">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8" t="s">
+      <c r="B33" s="7"/>
+      <c r="C33" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H33" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="14.4">
-      <c r="A34" s="7">
+    <row r="34" spans="1:8">
+      <c r="A34" s="6">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8" t="s">
+      <c r="B34" s="7"/>
+      <c r="C34" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E34" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="H34" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="14.4">
-      <c r="A35" s="7">
+    <row r="35" spans="1:8">
+      <c r="A35" s="6">
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C35" s="8"/>
-      <c r="D35" s="9" t="s">
+      <c r="C35" s="7"/>
+      <c r="D35" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="E35" s="10">
+      <c r="E35" s="9">
         <v>1</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="G35" s="9" t="s">
+      <c r="G35" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H35" s="9" t="s">
+      <c r="H35" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="14.4">
-      <c r="A36" s="7">
+    <row r="36" spans="1:8">
+      <c r="A36" s="6">
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="9" t="s">
+      <c r="C36" s="7"/>
+      <c r="D36" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E36" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="F36" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="G36" s="9" t="s">
+      <c r="G36" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H36" s="9" t="s">
+      <c r="H36" s="8" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2932,7 +2348,7 @@
     <mergeCell ref="A1:H2"/>
   </mergeCells>
   <pageMargins left="0.707638888888889" right="0.511805555555556" top="0.747916666666667" bottom="0.747916666666667" header="0.313888888888889" footer="0.313888888888889"/>
-  <pageSetup fitToHeight="0" orientation="landscape" paperSize="9" scale="10"/>
+  <pageSetup paperSize="9" scale="92" fitToHeight="0" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
